--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0058.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0058.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Wenmo</t>
+          <t>Văn Mặc</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Điều tra bức tranh</t>
+          <t>Xem bức tranh</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Daily Scoop</t>
+          <t>Tin Tức Hằng Ngày</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Lắp Đá Mỏ Neo</t>
+          <t>Chèn Đá Neo</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>: Jumbled Dreams</t>
+          <t>: Những Giấc Mơ Hỗn Độn</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Đặt một bình mật ong Hoàng Hôn</t>
+          <t>Bỏ lại một bình Mật Ong Hoàng Hôn</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Ký ức Chiến đấu</t>
+          <t>Ký Ức Chiến Đấu</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Heal</t>
+          <t>Hồi phục</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Hunter: Ice</t>
+          <t>Thợ Săn: Băng</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Tham gia "Bản sao của những ngày đã qua"</t>
+          <t>Vào "Replica of Past Days"</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Jingling</t>
+          <t>Kinh Linh</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Mutant Organism: Gulpuff</t>
+          <t>Sinh vật thể đột biến: Gulpuff</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Lazy Teen</t>
+          <t>Thiếu niên lười</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Phân tích ngăn chặn Ma trận Sao 1712</t>
+          <t>Phân Tích Kiểm Soát Ma Trận Sao 1712</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Enable Force Settlement</t>
+          <t>Bật Buộc Kết Toán</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Metaphor</t>
+          <t>Ẩn Dụ</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Logistics Specialist</t>
+          <t>Chuyên Gia Hậu Cần</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Airsailer</t>
+          <t>Thuyền Buồm Gió</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Crystal Cluster Giant</t>
+          <t>Người Khổng Lồ Cụm Pha Lê</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Fuyan</t>
+          <t>Phù Diễn</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Jiangpiao</t>
+          <t>Khương Phiêu</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Geospider S4</t>
+          <t>Nhện Địa Chấn S4</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Thiết bị Mourning Aix: Tiếng ồn</t>
+          <t>Thiết bị Mourning Aix: Tạp Âm</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Devotee's Flesh</t>
+          <t>Thịt Tín Đồ</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Chain</t>
+          <t>Dây Xích</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Dâng lễ chiến thắng</t>
+          <t>Dâng hiến chiến thắng</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Hình chiếu của Threnodian Aleph-1</t>
+          <t>Hiện Thân Aleph-1 của Threnodian</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Đài Phát Thanh</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Ferripaws</t>
+          <t>Móng Sắt</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Mingwu</t>
+          <t>Minh Vũ</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Touch</t>
+          <t>Chạm</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Hồi tưởng</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Đến Averardo Vault</t>
+          <t>Đến Hầm Averardo</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Đã vô hiệu hóa (mất kết nối nguồn điện)</t>
+          <t>Đã vô hiệu hóa (ngắt nguồn điện)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Grandino Gladiator</t>
+          <t>Đấu sĩ Grandino</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Jar</t>
+          <t>Lọ</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Medium-Sized Fishing Spot</t>
+          <t>Điểm Câu Cá Cỡ Vừa</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Touch</t>
+          <t>Chạm</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Cartethyia Cube</t>
+          <t>Khối Cartethyia</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Weathered Stele</t>
+          <t>Bia Đá Mòn Mỏi</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Fengxi</t>
+          <t>Phong Hy</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Fourth Floor</t>
+          <t>Tầng Bốn</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Candlestick Fairy</t>
+          <t>Tiên Nến</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>About Memory Manual</t>
+          <t>Về Sách Ký Ức</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Mulan</t>
+          <t>Mộc Lan</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Uncle Wei</t>
+          <t>Chú Vi</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Electric Blade</t>
+          <t>Lưỡi Kiếm Điện</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Jifeng</t>
+          <t>Tế Phong</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Wujing</t>
+          <t>Vô Tịnh</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Zig Zag: Light</t>
+          <t>Zig Zag: Sáng</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>To Third Floor</t>
+          <t>Đến Tầng Ba</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Xuanzhu</t>
+          <t>Huyên Trúc</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Dân thường đứng xem</t>
+          <t>Dân thường theo dõi</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Jovial Actor</t>
+          <t>Diễn Viên Vui Tính</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Kangjiu</t>
+          <t>Khang Cửu</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Tham gia thử thách Khủng Hoảng Ảo</t>
+          <t>Tham gia thử thách Virtual Crisis</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Tiếng gọi Vực Sâu</t>
+          <t>Tiếng Gọi Vực Sâu</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Shipwright Marco</t>
+          <t>Thợ đóng tàu Marco</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Phantom: Lightcrusher</t>
+          <t>Phantom: Đè Ánh Sáng</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Mortefi's Projection</t>
+          <t>Hình chiếu của Mortefi</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Little Namipons</t>
+          <t>Những Namipon Nhỏ</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Để lại một viên Complete Nutrition Squeezy Jelly</t>
+          <t>Bỏ lại một gói Dinh Dưỡng Toàn Diện Squeezy Jelly</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Right Runner</t>
+          <t>Người Chạy Bên Phải</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Cây cầu gỗ ở Thung Lũng Taoyuan</t>
+          <t>Cây cầu gỗ ở Thung Lũng Đào Nguyên</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Gather</t>
+          <t>Thu thập</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Crystal Cluster Warrior</t>
+          <t>Chiến Binh Cụm Pha Lê</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Điểm câu cá có khả năng câu được cá lớn</t>
+          <t>Điểm Câu Có Khả Năng Thu Hoạch Lớn</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Namipon Poster</t>
+          <t>Áp phích Namipon</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Investigate</t>
+          <t>Điều Tra</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Hurriclaw Alpha: Simulated Replica</t>
+          <t>Bão Vuốt Alpha: Bản Mô Phỏng</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Loot Chest</t>
+          <t>Rương Chiến Lợi Phẩm</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Synthesizer</t>
+          <t>Bộ tổng hợp</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Đến tầng dưới</t>
+          <t>Xuống tầng dưới</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Một bia mộ vây quanh bởi tiếng hú sói</t>
+          <t>Ngôi mộ vây quanh bởi tiếng hú sói</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>Xuyên thấu</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Bước vào Ký ức về Những Vì Sao</t>
+          <t>Bước vào Ký Ức Vì Sao</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Play Channel 1</t>
+          <t>Phát Kênh 1</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Thông báo Board</t>
+          <t>Bảng Thông Báo</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Chair</t>
+          <t>Ghế</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Organize</t>
+          <t>Tổ Chức</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Đến Huấn luyện (Tăng cường Nhân vật)</t>
+          <t>Đến Huấn Luyện (Nâng Cấp Nhân Vật)</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Pressure Platform</t>
+          <t>Nền Đỡ Áp Lực</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Hiệp sĩ của Sự phù phiếm</t>
+          <t>Hiệp Sĩ Hư Vinh</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Hiyuki's White Bird</t>
+          <t>Chim Trắng của Hiyuki</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Lotus Beast</t>
+          <t>Quái Thú Sen</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Cartethyia Cube</t>
+          <t>Khối Cartethyia</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Black Shores Hour-glass Pillar</t>
+          <t>Trụ Đồng Hồ Cát Bờ Đen</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Xiaoju</t>
+          <t>Tiểu Cúc</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Bóng Ma: Lớp Vỏ Lò Phản Ứng</t>
+          <t>Hồn Ma: Xác Sống Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Rời kho Cassette</t>
+          <t>Rời Kho Lưu Trữ Băng Cassette</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Frostscourge Stalker</t>
+          <t>Kẻ Rình Rập Băng Giá</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Voidspawn: Shadow Stepper</t>
+          <t>Voidspawn: Bước Ảnh Vô Hình</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Công dân Đắm chìm Hoàn toàn</t>
+          <t>Công Dân Hoàn Toàn Hòa Nhập</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Người Bảo vệ Lưu trữ</t>
+          <t>: Người Gác Kho Lưu Trữ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Feathered Ice Cubes</t>
+          <t>Băng Khối Lông Vũ</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Jinhu</t>
+          <t>Jinhu...</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Gravity Calibrator</t>
+          <t>Bộ Điều Chỉnh Trọng Lực</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Jinhsi Cube</t>
+          <t>Khối Kim Tư</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Lời mời thách đấu</t>
+          <t>Mời thách đấu</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>: "Timid Lion"</t>
+          <t>: "Sư Tử Nhút Nhát"</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Weight-carrying Youth</t>
+          <t>Tuổi Trẻ Gánh Vác</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Wu Sheng</t>
+          <t>Ngộ Sinh</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>The Mirror Self</t>
+          <t>Bản Ngã Trong Gương</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Lamentation Flower Seed</t>
+          <t>Hạt Giống Hoa Than Thở</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Strange Passerby</t>
+          <t>Người Qua Đường Kỳ Lạ</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Judgement: Terminatation</t>
+          <t>Phán Quyết: Thanh Trừng</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Tiger's Maw Food Stalls</t>
+          <t>Khu Ẩm Thực Hàm Hổ</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Console</t>
+          <t>Bảng điều khiển</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Chromeshell</t>
+          <t>Vỏ Sắc</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Discord: Hoochief: Elite: Wind</t>
+          <t>Tacet Discord: Hoochief: Elite: Wind</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Điều tra màn hình desktop</t>
+          <t>Kiểm tra máy tính để bàn</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>: Ruthless Fury</t>
+          <t>: Cơn Thịnh Nộ Tàn Bạo</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Phantom: Twin Nova Collapsar Blade</t>
+          <t>Phantom: Song Tinh Vân Kiếm Hố Đen</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Mingyi</t>
+          <t>Minh Nghi</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Thử thách Nhận thức III</t>
+          <t>Thử Thách Nhận Thức III</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Thay đổi vũ khí đang trưng bày</t>
+          <t>Đổi vũ khí hiển thị</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Chuji</t>
+          <t>Chu ji</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Insufficient Stability</t>
+          <t>Không đủ Độ Ổn Định</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Chongwang</t>
+          <t>Sùng Vượng</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>: Lingering Storm</t>
+          <t>: Bão Tàn Dư</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Ninja Namipon</t>
+          <t>Namipon Ninja</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Khu vực đăng ký rơi</t>
+          <t>khu vực đăng ký rơi tự do</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Carlotta Cube</t>
+          <t>Khối Carlotta</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Rời khỏi</t>
+          <t>Rời đi</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Misha's Message</t>
+          <t>Tin Nhắn Của Misha</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Đế từ tính lơ lửng</t>
+          <t>Nền Magnetit Bay Lượn</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Quiet Acolyte</t>
+          <t>Tín Đồ Lặng Lẽ</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Thành viên Montelli Điềm tĩnh</t>
+          <t>Thành viên Montelli điềm tĩnh</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Dripsnail</t>
+          <t>Ốc Sên Nhỏ Giọt</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Tank Guardian: Fire</t>
+          <t>Hộ Vệ Thiết Giáp: Hỏa Diệm</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Uncle Hong</t>
+          <t>Chú Hồng</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Chuck</t>
+          <t>Chút</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>: Delusion Whispers</t>
+          <t>: Lời Thì Thầm Ảo Giác</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Tiến vào Chiến đấu (Ẩn dụ)</t>
+          <t>Bước vào trận chiến</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Destructible Wooden Crate</t>
+          <t>Thùng gỗ có thể phá hủy</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Người đàn ông tốt bụng</t>
+          <t>Người Đàn Ông Tốt Bụng</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Telephone Booth</t>
+          <t>Buồng điện thoại công cộng</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Mở lồng</t>
+          <t>Mở lồng ra đi</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Đứa trẻ nghiêm túc</t>
+          <t>Đứa Trẻ Nghiêm Túc</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Người chăn cừu già</t>
+          <t>Mục Đồng Già</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Jiming</t>
+          <t>Tập Minh</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Echo Discord: Sóng Tacet Vỡ</t>
+          <t>Tổ Tacet Discord: Sóng Tacet Vỡ</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Lecture Hall</t>
+          <t>Giảng đường</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Cô gái Royan</t>
+          <t>Cô gái Roya</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Người phụ nữ hoạt bát</t>
+          <t>Cô gái sôi nổi</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Tham gia "Thử thách Giả mạo"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Hieros</t>
+          <t>Hieron</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Cô gái vui vẻ</t>
+          <t>Cô Gái Vui Vẻ</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Zhenjian</t>
+          <t>Chân Kiếm</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Nhật ký Cuối Cùng</t>
+          <t>Nhật Ký Cuối</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Qisheng</t>
+          <t>Khởi Sinh</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Shuhe</t>
+          <t>Thủy Hạ</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Blue Rain</t>
+          <t>Mưa Xanh</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Crimson Throne</t>
+          <t>Ngai Vàng Đỏ Thẫm</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Stone Lift - Group</t>
+          <t>Nâng Đá - Nhóm</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tiến vào Endstate Matrix</t>
+          <t>Bước vào Ma Trận Trạng Thái Cuối</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Mutant Organism: Excarat</t>
+          <t>Sinh vật thể đột biến: Excarat</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>"Caged Beast"</t>
+          <t>"Thú Hoang Trong Lồng"</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>First Floor</t>
+          <t>Tầng Đầu Tiên</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Zhonglin</t>
+          <t>Trùng Lâm</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Bowtie Butler</t>
+          <t>Quản Gia Nơ Bướm</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Golden-ringed Dragonfly</t>
+          <t>Chuồn Chuồn Vàng Vòng</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Hoverdroid</t>
+          <t>Robot Bay Lượn</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Appreciative Passerby</t>
+          <t>Người Qua Đường Biết Ơn</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Phrolova Disappear Special Effect</t>
+          <t>Hiệu ứng biến mất đặc biệt của Phrolova</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Huowen</t>
+          <t>Hỏa Văn</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Rusty Weapon</t>
+          <t>Vũ Khí Gỉ Sét</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Rời Command Rise</t>
+          <t>Rời Tháp Chỉ Huy</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Về người cao tuổi</t>
+          <t>Về Người Già</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Mi</t>
+          <t>Mi…</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Bóng tối Hoàng hôn</t>
+          <t>: Bóng Tối Chạng Vạng</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Asphodel Barrens Chụp ảnh Spot</t>
+          <t>Điểm Chụp Ảnh Đồng Bằng Asphodel</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Trash Can</t>
+          <t>Thùng Rác</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Kiểm tra sổ phác thảo</t>
+          <t>Kiểm tra cuốn sổ phác thảo</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Fengqin</t>
+          <t>Phong Cầm</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Laurus Sprouts</t>
+          <t>Mầm Laurus</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Cheerful Newcomer</t>
+          <t>Lính Mới Vui Vẻ</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Tiếp tục Exploration</t>
+          <t>Tiếp tục khám phá</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Galescourge Stalker</t>
+          <t>Thợ Săn Gale Scourge</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Mysterious Passerby</t>
+          <t>Người Qua Đường Bí Ẩn</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Fractsidus Gunmaster</t>
+          <t>Bậc Thầy Súng Fractsidus</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Kích hoạt Prototype Reactor Drive</t>
+          <t>Kích hoạt Động cơ Phản ứng Nguyên mẫu</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Abyssal Patricius</t>
+          <t>Quý Tộc Vực Sâu</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Uống nước</t>
+          <t>Uống nước đi</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Strange Cardboard Box</t>
+          <t>Thùng Giấy Kỳ Lạ</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Tôi hầu như không thấy được vị trí thiết bị</t>
+          <t>Tôi gần như không nhìn thấy vị trí của thiết bị.</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Nightmare: Feilian Beringal</t>
+          <t>Ác Mộng: Feilian Beringal</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Đến Lahai-Roi</t>
+          <t>Đến Lahai-Roi đi</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>"Cánh cửa Đoàn kết"</t>
+          <t>"Cánh Cửa Đoàn Kết"</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Dungeon Switch</t>
+          <t>Chuyển đổi Hầm</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Crowbar</t>
+          <t>Xà Beng</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Uncle Yun</t>
+          <t>Chú Vân</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Liên lạc với Lucilla</t>
+          <t>Liên hệ Lucilla</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Enter Whimpering Waste</t>
+          <t>Bước vào Vùng Đất Than Thở</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu hay tranh cãi</t>
+          <t>Nhà Nghiên Cứu Hay Cãi Nhau</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Học sinh điềm tĩnh</t>
+          <t>Học sinh trầm tĩnh</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Mount</t>
+          <t>Lên xe</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Jichen</t>
+          <t>Tế Trần</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Nightmare: Hecate</t>
+          <t>Ác Mộng: Hecate</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Mining Drone</t>
+          <t>Drone Khai Thác</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Lá cờ Chiến thắng</t>
+          <t>Ngọn Cờ Chiến Thắng</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Yi Dian</t>
+          <t>Nhất Điểm</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Fangdong</t>
+          <t>Phương Đông</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Rời Resounding Rise</t>
+          <t>Rời khỏi Resounding Rise</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Oil Painting</t>
+          <t>Bức Tranh Dầu</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Scavenger's Túi đồ</t>
+          <t>Ba Lô Kẻ Nhặt Nhạnh</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Chronopin</t>
+          <t>Kim Thời Gian</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Thunder Mage</t>
+          <t>Pháp Sư Sấm Sét</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>KU-Roro Mũ Chóp Cao</t>
+          <t>Lanxiang Desert</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Dingyin</t>
+          <t>Đinh Âm</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Gọi thang máy</t>
+          <t>Gọi Thang Máy</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>KU-Water</t>
+          <t>KU-Nước</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Casually Jotted Down Snack List</t>
+          <t>Danh Sách Đồ Ăn Vặt Ghi Vội</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đến Lahai-Roi giữa Bão Hư Không</t>
+          <t>Đến Lahai-Roi giữa cơn Bão Hư Không</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Ningwei</t>
+          <t>Ninh Vệ</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Vào Vương quốc Giai điệu</t>
+          <t>Bước vào Vương Quốc Giai Điệu.</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Foxtail Kelp</t>
+          <t>Rong Biển Foxtail</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Lặp lại chỉ dẫn</t>
+          <t>Lặp lại chỉ thị</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Người Đàn Ông Say Xỉn</t>
+          <t>Gã Say Rượu</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Play "Voyaging Star's Farewell"</t>
+          <t>Phát "Lời Tạm Biệt Của Ngôi Sao Hành Trình"</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Uncle Jiang</t>
+          <t>Bác Giang</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Kiểm tra thứ Roccia tìm thấy</t>
+          <t>Kiểm tra thứ Roccia tìm được</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Ruins</t>
+          <t>Tàn Tích</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Phantom: Crownless</t>
+          <t>Bóng Ma: Crownless</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Activate</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Ân Sủng</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32424,8 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Ông Già Bí Ẩn
-NAME_TITLE_00403:::Nhà Nghiên Cứu Soliskin Mới</t>
+          <t>Ông Già Bí Ẩn</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32495,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Uncle Gao</t>
+          <t>Chú Cao</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32635,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Repeater</t>
+          <t>Bộ lặp</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32705,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Summer Flower</t>
+          <t>Hoa Mùa Hạ</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32775,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Soliskin New</t>
+          <t>Nhà Nghiên Cứu Soliskin Mới</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32985,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Giao "Món Quà" mà hồn ma yêu cầu</t>
+          <t>Giao "Món Quà" mà hồn ma yêu cầu đi</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33195,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Đến vị trí Động Cơ Phản Ứng rơi xuống</t>
+          <t>Đến nơi Bộ Phản Ứng Lõi rơi xuống</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33265,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Roguelike Swimming Ring</t>
+          <t>Phao Bơi Roguelike</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Kính màu bên trái</t>
+          <t>Mảnh Kính Màu Bên Trái</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33405,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Lu Shen</t>
+          <t>Lữ Thâm</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33475,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Lollo Campaign Event Overview</t>
+          <t>Tổng quan sự kiện Chiến dịch Lollo</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33545,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>About Pinwen</t>
+          <t>Về Pinwen</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33615,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Faithful Follower</t>
+          <t>Kẻ Trung Thành</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33685,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Corroder</t>
+          <t>Kẻ Ăn Mòn</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -34105,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Lãnh Đạo Lưu Đày</t>
+          <t>Thủ Lĩnh Lưu Đày</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34525,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Yunqi</t>
+          <t>Vân Khí</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34595,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Liuqin</t>
+          <t>Lục Cầm</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34665,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Thực Đơn Đồ Uống</t>
+          <t>Danh sách đồ uống</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34735,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Người Dân Đi Dạo</t>
+          <t>Dân Dạo Chơi</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34805,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Fuyue</t>
+          <t>Phù Việt</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34875,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Ngồi vào ghế gần mũi tàu</t>
+          <t>Ngồi ghế gần mũi tàu đi</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34945,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Rusty Axe</t>
+          <t>Rìu Gỉ</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35015,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Cô Gái Trẻ</t>
+          <t>Cô Bé</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35155,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Excited Audience</t>
+          <t>Khán Giả Phấn Khích</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35225,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Trở Lại Mặt Tối</t>
+          <t>Trở lại Bóng Tối</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35435,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Xiaoshi</t>
+          <t>Tiểu Thạch</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35505,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Xiaobei</t>
+          <t>Tiểu Bối</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
